--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_03_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_03_19_Cau.xlsx
@@ -933,7 +933,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người dùng cần biết làm gì khác ở mỗi trạng thái.</t>
+          <t>Hành vi phù hợp theo ba mức độ tin cậy đã hiệu chỉnh: Độ tin cậy cao: hiện kết quả và nguồn, người dùng có thể chấp nhận (a); Độ tin cậy trung bình: nói rõ chưa chắc chắn, hiện lựa chọn khác và yêu cầu người dùng kiểm tra (b); Độ tin cậy thấp: không tự thực hiện hành động, chuyển sang phương án dự phòng hoặc người xử lý (d).</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người kiểm tra phải tái tạo được AI đã sai gì và dữ liệu chỉnh sửa được dùng ở đâu.</t>
+          <t>Bản ghi tín hiệu chỉnh sửa đầy đủ cần: Mã giao dịch và đặc trưng đầu vào (a), Nhãn AI trước khi sửa (b), Nhãn người dùng chọn sau khi sửa (c), Mã sự kiện chỉnh sửa liên kết các bản ghi (d), và Nơi sử dụng dữ liệu để đánh giá/cải thiện (f).</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ba lỗi có thể quan trọng hơn mười lỗi nếu hậu quả khác nhau.</t>
+          <t>Trong 13 lỗi của bộ phân loại email, 3 email VIP bị phân loại nhầm vào Spam gây mất thương vụ có hậu quả nghiêm trọng hơn nhiều so với 10 email FYI vào Updates. Ưu tiên can thiệp đúng là nhóm VIP→Spam dựa trên mức độ nghiêm trọng của hậu quả.</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không phát hành thay đổi trước khi qua bước đánh giá.</t>
+          <t>Vòng phản hồi cải thiện hệ thống: Thu thập chỉnh sửa có dấu vết (o2) -&gt; Phân tích mẫu lỗi (o4) -&gt; Thay đổi prompt/dữ liệu/UX (o5) -&gt; Đánh giá thay đổi trên bộ kiểm thử cố định (o1) -&gt; Quan sát hành vi mới sau khi triển khai (o3).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_03_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_05_Full_78_Cau/Day_05_Ngan_Hang_Phan_03_19_Cau.xlsx
@@ -674,10 +674,27 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Fallback là hành vi quan sát được, không phải nhãn chung.
-Phân tích theo nguyên lý thiết kế: Fallback là hành vi quan sát được, không phải nhãn chung.</t>
+- 1.0 điểm: Thiết kế Fallback 1 kích hoạt chính xác khi điểm tin cậy thấp hoặc phân vân giữa các nhãn.
+- 1.0 điểm: Mô tả hành vi quan sát được của Fallback 1 (gợi ý tham khảo, mở dropdown cho người dùng tự chọn thủ công).
+- 1.0 điểm: Thiết kế Fallback 2 kích hoạt chính xác khi phát hiện nội dung pháp lý nhạy cảm.
+- 1.0 điểm: Mô tả hành vi của Fallback 2 (khóa tự động, định tuyến sang chuyên viên pháp chế có thẩm quyền).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hai Phương án Dự phòng (Fallback Modes) cho Tính năng Gợi ý Nhãn Tài liệu:
+1. Phương án Dự phòng 1: Dự phòng Độ tin cậy thấp (Low-Confidence Fallback - Graceful Degradation)
+- Điều kiện kích hoạt: Điểm số tin cậy do mô hình dự báo nằm dưới ngưỡng an toàn (`confidence_score &lt; 0.65`) hoặc phân phối xác suất giữa hai nhãn cao nhất quá suýt soát (`top1_prob - top2_prob &lt; 0.15`).
+- Trạng thái và Hành vi hiển thị cho người dùng:
+  + Giao diện KHÔNG tự động điền sẵn nhãn vào tài liệu để tránh tạo thiên kiến sai lệch.
+  + Hiển thị thông báo nhẹ nhàng: 'AI chưa chắc chắn về nhãn của tài liệu này. Gợi ý tham khảo: [Nhãn A] hoặc [Nhãn B]'.
+  + Mở sẵn danh sách thả xuống (dropdown) toàn bộ danh mục nhãn để người dùng tự tay chọn thủ công chỉ với một thao tác nhấp chuột.
+2. Phương án Dự phòng 2: Dự phòng An toàn Pháp lý Nhạy cảm (High-Risk Legal Content Fallback - Human-in-the-Loop Routing)
+- Điều kiện kích hoạt: Bộ quét từ khóa quy chuẩn và bộ phân loại an toàn phát hiện tài liệu có chứa nội dung pháp lý nhạy cảm, dữ liệu tài chính mật hoặc điều khoản tranh chấp tố tụng (`legal_risk_flag == True`).
+- Trạng thái và Hành vi hiển thị cho người dùng:
+  + Khóa tính năng tự động gắn nhãn thông thường; hiển thị huy hiệu bảo mật: 'Tài liệu chứa điều khoản pháp lý cần kiểm duyệt chuyên môn'.
+  + Bước tiếp theo hiển thị cho người dùng: Nút bấm 'Gửi đến Chuyên viên Pháp chế thẩm định'. Tài liệu được tự động chuyển vào hàng đợi kiểm duyệt riêng của bộ phận pháp chế; người dùng được cấp mã theo dõi tiến độ thẩm định.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Fallback trong sản phẩm AI không phải là một thông báo lỗi chết mà là một hành vi quan sát được có tính chuyển tiếp nhịp nhàng. Đối với lỗi không chắc chắn về dữ liệu (Low confidence), sản phẩm chuyển quyền chủ động nhẹ nhàng cho người dùng cuối. Đối với rủi ro pháp lý cao, sản phẩm bắt buộc phải định tuyến sang chuyên gia có thẩm quyền phù hợp.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Designing Graceful Fallbacks &amp; Human-in-the-Loop AI Architecture Patterns (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -757,10 +774,40 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nếu luồng chưa nói người dùng thấy gì và đi đâu tiếp thì chưa hoàn chỉnh.
-Phân tích theo nguyên lý thiết kế: Nếu luồng chưa nói người dùng thấy gì và đi đâu tiếp thì chưa hoàn chỉnh.</t>
+- 1.0 điểm: Đặc tả Luồng chuẩn (Happy Path) đầy đủ 5 thành tố (kích hoạt, giao diện, hành động, trạng thái sau, telemetry).
+- 1.0 điểm: Đặc tả Luồng ngoại lệ (Edge Path) khi gặp email nhiều chủ đề với bước phân định rõ ràng.
+- 1.0 điểm: Đặc tả Luồng lỗi (Error Path) khi gặp lỗi hạ tầng với giao diện phục hồi không gây bế tắc.
+- 1.0 điểm: Đặc tả Luồng phục hồi (Recovery Path) khi người dùng từ chối bản nháp kèm các tùy chọn chỉnh sửa thông minh.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Quy ước Bốn Luồng Hành vi (Four-Path Behavior Contract) cho AI Tạo Bản nháp Email:
+1. Luồng Chuẩn (Happy Path):
+- Điều kiện kích hoạt: Người dùng chọn 1 email có nội dung rõ ràng và bấm 'Soạn nháp'; không có thông tin khuyết thiếu.
+- Trạng thái người dùng thấy: Giao diện hiển thị bản nháp hoàn chỉnh trong khung soạn thảo với nhãn 'Bản nháp do AI đề xuất'.
+- Hành động của người dùng: Đọc lướt, có thể chỉnh sửa nhẹ, và bấm 'Gửi thư'.
+- Trạng thái tiếp theo: Email được gửi đi; hiển thị thông báo 'Đã gửi thành công'.
+- Tín hiệu tối thiểu ghi nhận: `event: 'draft_sent_without_major_edits'`, `edit_distance_ratio &lt; 0.2`.
+2. Luồng Ngoại lệ / Biên (Edge Path):
+- Điều kiện kích hoạt: Email nhận được có nội dung rất dài hoặc chứa 3 chủ đề thảo luận khác nhau.
+- Trạng thái người dùng thấy: AI hiển thị thông báo chọn lọc: 'Email này thảo luận 3 chủ đề. Bạn muốn trả lời về: [Chủ đề 1], [Chủ đề 2] hay [Cả ba]?'.
+- Hành động của người dùng: Chọn chủ đề mong muốn.
+- Trạng thái tiếp theo: AI sinh bản nháp tập trung vào đúng chủ đề được chọn.
+- Tín hiệu tối thiểu ghi nhận: `event: 'multi_topic_disambiguation_selected'`, `selected_topic_id`.
+3. Luồng Lỗi (Error Path):
+- Điều kiện kích hoạt: Mất kết nối internet hoặc API của nhà cung cấp LLM trả về mã lỗi 503/Timeout.
+- Trạng thái người dùng thấy: Hiển thị thanh thông báo lỗi màu vàng: 'Không thể kết nối với trợ lý AI. Chúng tôi đã mở sẵn khung soạn thảo trống để bạn không bị gián đoạn công việc'.
+- Hành động của người dùng: Bấm nút 'Thử lại' hoặc tự gõ nội dung thư.
+- Trạng thái tiếp theo: Hệ thống thử kết nối lại hoặc lưu nội dung người dùng tự gõ.
+- Tín hiệu tối thiểu ghi nhận: `event: 'ai_service_error'`, `error_code: 503`, `fallback_to_manual: true`.
+4. Luồng Phục hồi (Recovery Path):
+- Điều kiện kích hoạt: Người dùng không ưng ý với bản nháp vừa tạo (bấm nút 'Không dùng bản nháp này' hoặc xóa toàn bộ văn bản).
+- Trạng thái người dùng thấy: Hộp thoại khôi phục hiển thị: 'Bạn muốn điều chỉnh điều gì? [Ngắn gọn hơn] [Trang trọng hơn] [Đổi ý chính] hoặc [Tự viết]'.
+- Hành động của người dùng: Chọn nút 'Ngắn gọn hơn'.
+- Trạng thái tiếp theo: AI tạo lại bản nháp mới cô đọng hơn mà không làm mất thông tin người nhận.
+- Tín hiệu tối thiểu ghi nhận: `event: 'draft_rejected_and_recovered'`, `recovery_action: 'shorten'`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một hợp đồng hành vi bốn luồng (Four-Path Behavior Contract) chuẩn mực quy định rõ ràng ma trận tương tác: Kích hoạt -&gt; Giao diện hiển thị -&gt; Hành động người dùng -&gt; Chuyển trạng thái -&gt; Telemetry log. Điều này giúp đội ngũ kỹ thuật và thiết kế thống nhất chính xác cách xử lý từ trường hợp lý tưởng đến trường hợp phục hồi sai sót.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Four Paths Framework &amp; State Machine Patterns for AI User Experience (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -791,10 +838,21 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nói rõ cả việc AI làm được và việc người dùng vẫn phải chịu trách nhiệm.
-Phân tích theo nguyên lý thiết kế: Nói rõ cả việc AI làm được và việc người dùng vẫn phải chịu trách nhiệm.</t>
+- 1.0 điểm: Nêu rõ ràng khả năng của công cụ (ưu tiên hồ sơ tiếng Việt dạng văn bản).
+- 1.0 điểm: Nêu dứt khoát ranh giới giới hạn (không tự ý loại ứng viên, không hỗ trợ ngoại ngữ khác/ảnh quét).
+- 1.0 điểm: Chỉ rõ bước tiếp theo và khẳng định quyền quyết định cuối cùng thuộc về chuyên viên HR.
+- 1.0 điểm: Văn phong chuyên nghiệp, súc tích trong đúng dung lượng 2-3 câu hướng dẫn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Soạn thảo 2–3 câu hướng dẫn mở đầu (Onboarding &amp; Capability Expectation Communication):
+"Chào bạn! Công cụ AI này hỗ trợ bạn tự động đọc và sắp xếp thứ tự ưu tiên các hồ sơ ứng viên bằng tiếng Việt dạng văn bản dựa trên mức độ phù hợp với mô tả công việc. Xin lưu ý: Hệ thống chỉ đóng vai trò trợ lý gợi ý xếp hạng ban đầu và tuyệt đối không có quyền tự ý loại bỏ bất kỳ ứng viên nào, đồng thời chưa hỗ trợ đánh giá các CV bằng ngôn ngữ khác hoặc định dạng hình ảnh quét. Bạn vui lòng xem xét kỹ hồ sơ chi tiết và đưa ra quyết định tuyển dụng cuối cùng."
+Phân tích tính chuẩn mực của đoạn hướng dẫn:
+- Nêu rõ khả năng (What it can do): Đọc và ưu tiên hồ sơ CV tiếng Việt dạng văn bản theo JD.
+- Nêu rõ ranh giới giới hạn (What it cannot do): Không tự loại hồ sơ, không hỗ trợ ngôn ngữ khác ngoài tiếng Việt, không đọc CV ảnh quét mờ.
+- Xác định rõ bước tiếp theo và trách nhiệm (Next step &amp; Accountability): Nhắc nhở HR luôn là người giữ quyền quyết định tuyển dụng cuối cùng (Human accountability).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kỹ thuật Capability Expectation Communication trong thiết kế AI nhằm hiệu chỉnh mô hình tâm lý (mental model) của người dùng ngay từ lần tiếp xúc đầu tiên. Việc truyền thông trung thực cả năng lực và ranh giới giới hạn giúp loại bỏ kỳ vọng hão huyền, ngăn chặn tình trạng ỷ lại mù quáng vào AI (over-reliance) và bảo vệ trách nhiệm đạo đức của con người trong các quyết định tuyển dụng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Microsoft HAX Toolkit (Human-AI eXperience) - Guideline 1: Make clear what the system can do &amp; Guideline 2: Make clear how well the system can do what it can do (https://www.microsoft.com/en-us/research/project/guidelines-for-human-ai-interaction/)</t>
         </is>
       </c>
     </row>
@@ -876,10 +934,24 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giải thích tốt phải có thể thay đổi hành động của người quản lý.
-Phân tích theo nguyên lý thiết kế: Giải thích tốt phải có thể thay đổi hành động của người quản lý.</t>
+- 1.0 điểm: Chọn đúng kiểu giải thích phản thực tế tương tác (Counterfactual / What-If Scenario simulation).
+- 1.0 điểm: Thiết kế hiển thị bằng chứng định lượng gắn liền với quyết định tồn kho (mùa vụ, khuyến mãi, chi phí lưu kho).
+- 1.0 điểm: Cung cấp cơ chế tương tác thử nghiệm điều chỉnh biến số (giảm 20% khuyến mãi -&gt; lượng tồn kho thay đổi tương ứng).
+- 1.0 điểm: Chỉ ra dứt khoát những thứ không được lộ (trọng số ma trận toán học, mã log kỹ thuật thô).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn kiểu giải thích (Explanation Pattern):
+- Kiểu giải thích: Giải thích dựa trên Kịch bản giả định / Phản thực tế tương tác (Interactive Counterfactual &amp; Scenario-based Explanation / 'What-If' Simulation).
+2. Bằng chứng cụ thể hiển thị trên giao diện cho Quản lý:
+- Hiển thị các biến số đầu vào chi phối quyết định: 'Dự báo nhu cầu tăng +35% dựa trên dữ liệu lịch sử mùa vụ cùng kỳ năm ngoái (+20%) kết hợp với chương trình khuyến mãi sắp tới (+15%)'.
+- Thanh trượt giả định tương tác (Interactive Slider): Cho phép quản lý trực tiếp kéo giảm chương trình khuyến mãi xuống mức -20% để xem ngay phản ứng của mô hình: 'Nếu áp dụng giảm giá 20%, nhu cầu dự báo sẽ điều chỉnh từ +35% xuống còn +18%, tương ứng mức tồn kho an toàn khuyến nghị giảm từ 500 thùng xuống 320 thùng'.
+- Tác động tài chính rõ ràng: Hiển thị ước tính chi phí lưu kho phát sinh vs tổn thất cơ hội nếu thiếu hàng bán.
+3. Điều TUYỆT ĐỐI KHÔNG NÊN LỘ trên giao diện:
+- Không hiển thị các trọng số ma trận toán học phức tạp (neuron weights), tensor embeddings hay công thức hồi quy/deep learning nội tại của mô hình.
+- Không hiển thị các mã log kỹ thuật thô hay các tham số toán học gây quá tải nhận thức và làm rối loạn khả năng ra quyết định nghiệp vụ của người quản lý.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Đối với người quản lý kinh doanh, một lời giải thích hữu ích không phải là việc giải thích cấu trúc mạng nơ-ron (Technical transparency) mà là khả năng giải thích hành động (Actionable explainability) qua kịch bản 'What-If'. Cho phép người dùng tương tác với các giả định (như giảm giá 20%) giúp họ kiểm chứng logic của AI và tự tin đưa ra quyết định phê duyệt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Explainability + Trust (https://pair.withgoogle.com/guidebook/patterns/explainability/) &amp; DARPA XAI Principles</t>
         </is>
       </c>
     </row>
@@ -965,10 +1037,23 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Điểm số thô chưa cho biết xác suất đúng hay ngưỡng hành động.
-Phân tích theo nguyên lý thiết kế: Điểm số thô chưa cho biết xác suất đúng hay ngưỡng hành động.</t>
+- 1.0 điểm: Từ chối hiển thị con số thô 0.71 chưa hiệu chỉnh vì gây hiểu lầm xác suất.
+- 1.0 điểm: Thiết kế trạng thái hiển thị trung thực dạng cảnh báo cần rà soát (`CẦN_XÁC_MINH_THỦ_CÔNG`).
+- 1.0 điểm: Thiết kế trực quan hỗ trợ đối chiếu (đánh dấu ô nghi vấn, đặt ảnh gốc song song).
+- 1.0 điểm: Khóa cổng thanh toán tự động, bắt buộc kế toán xác nhận thủ công trước khi chuyển tiền.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Trạng thái Hiển thị Trung thực (Honest Presentation State):
+- Tuyệt đối KHÔNG hiển thị số thô 'Độ tin cậy: 71%' trực tiếp cho người dùng (vì điểm số 0.71 chưa được hiệu chỉnh - uncalibrated confidence score, không đại diện cho xác suất 71% chính xác và không có ý nghĩa hành động đối với người làm kế toán/thanh toán).
+- Trạng thái hiển thị trung thực được gán nhãn: `CẦN_XÁC_MINH_THỦ_CÔNG` (Review Required) kèm màu cảnh báo vàng hổ phách (amber).
+- Thông điệp hiển thị trên giao diện: 'Dữ liệu hóa đơn này có một số chi tiết mờ hoặc chưa chắc chắn. Để đảm bảo tính chính xác trong thanh toán, vui lòng đối chiếu và xác nhận lại các trường thông tin được đánh dấu bên dưới'.
+- Đánh dấu trực quan (Visual Highlighting): Bôi viền vàng xung quanh các ô thông tin nhạy cảm có độ tin cậy thấp (như Tổng tiền thanh toán, Số tài khoản thụ hưởng, Mã số thuế) và đặt ảnh chụp hóa đơn gốc song song ngay bên cạnh.
+2. Hành động tiếp theo bắt buộc đối với người dùng (Next Required Actions):
+- Hành động 1: Người dùng bắt buộc phải bấm chuột vào ô thông tin để kiểm tra và xác nhận giá trị đúng trước khi hệ thống kích hoạt nút 'Tiếp tục'.
+- Hành động 2: Khóa hoàn toàn nút 'Thanh toán tự động'; chỉ cho phép chuyển sang trạng thái thanh toán khi có sự xác nhận chủ động bằng tay của kế toán viên.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong các bài toán có hậu quả tài chính trực tiếp (Financial/Payment Consequences), điểm tin cậy chưa được hiệu chuẩn (Uncalibrated score) không được phép biến thành tấm bình phong tạo cảm giác an tâm giả tạo. Hệ thống phải chuyển dịch từ việc 'báo điểm số' sang 'hướng dẫn hành vi' thông qua việc yêu cầu đối chiếu song song và khóa cổng thanh toán tự động.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Calibrating Trust &amp; Designing for Uncertainty in High-Stakes Domains (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -1053,10 +1138,23 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Cùng là con người nhưng bốn vai trò tạo bốn đầu ra khác nhau.
-Phân tích theo nguyên lý thiết kế: Cùng là con người nhưng bốn vai trò tạo bốn đầu ra khác nhau.</t>
+- 1.0 điểm: Lập bảng phân công đầy đủ 5 vai trò (AI và 4 vai trò người: CS, Quản lý, QA, Chuyên viên gian lận).
+- 1.0 điểm: Phân định ranh giới thẩm quyền chính xác theo điều kiện kích hoạt (&lt;=5tr vs &gt;5tr vs gian lận).
+- 1.0 điểm: Xác định đúng dữ liệu thông tin cần tiếp cận cho từng vị trí.
+- 1.0 điểm: Xác định đúng đầu ra nghiệp vụ riêng biệt của từng vai trò (duyệt, ký ngoại lệ, gắn thẻ QA, phong tỏa tài khoản).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Bảng Ma trận Phân công Vai trò Người - AI trong Luồng Hoàn tiền (Human-AI Role Assignment Matrix):
+| Vai trò | Điều kiện kích hoạt | Thẩm quyền ra quyết định | Thông tin cần tiếp cận | Hành động &amp; Đầu ra cụ thể |
+| :--- | :--- | :--- | :--- | :--- |
+| **Hệ thống AI** | Khách hàng gửi yêu cầu hoàn tiền | Tự động đề xuất, không có quyền duyệt cuối | Đơn hàng, lịch sử mua sắm, lý do hoàn tiền, chính sách hoàn tiền | Trích xuất dữ liệu, kiểm tra quy tắc ban đầu, xuất `Đề xuất hoàn tiền` kèm điểm tin cậy |
+| **Nhân viên hỗ trợ (CS Agent)** | Có đề xuất hoàn tiền từ AI cho khoản chi &lt;= 5 triệu | Quyết định chấp thuận hoặc từ chối các khoản hoàn tiền &lt;= 5 triệu | Đề xuất của AI, ảnh chụp sản phẩm lỗi, lịch sử chat của khách | Xác minh tính hợp lệ của chính sách, bấm `Duyệt hoàn tiền` (&lt;=5tr) hoặc `Từ chối` (kèm lý do) |
+| **Quản lý (Manager)** | Khoản tiền đề xuất hoàn trả &gt; 5 triệu VNĐ | Quyết định phê duyệt hoặc từ chối các khoản ngoại lệ có giá trị cao | Hồ sơ hoàn tiền, bằng chứng lỗi, lý do đề xuất từ nhân viên CS | Thẩm định ngân sách rủi ro, ký điện tử phê duyệt `Chấp thuận chi trả ngoại lệ` (&gt;5tr) |
+| **Đội ngũ QA (Quality Assurance)** | Mẫu ngẫu nhiên hoặc sau khi có khiếu nại quyết định sai | Đánh giá tính tuân thủ quy trình, không can thiệp tiền của khách | Toàn bộ log hội thoại, đề xuất AI, thao tác của CS, quy định chuẩn | Gắn nhãn nguyên nhân gốc rễ cho quyết định sai (`Gắn Root-Cause Tag`), xuất báo cáo kiểm định chất lượng |
+| **Chuyên viên Gian lận (Fraud Specialist)** | Hệ thống phát hiện dấu hiệu bất thường (nhiều tài khoản chung 1 thẻ, hoàn tiền liên tục) | Quyết định phong tỏa tài khoản và từ chối vĩnh viễn giao dịch | Lịch sử thiết bị, IP, mạng lưới liên kết tài khoản ngân hàng, mẫu gian lận | Tiến hành điều tra chuyên sâu, ban hành quyết định `Phong tỏa / Đưa vào danh sách đen (Blacklist)` |
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong các quy trình nghiệp vụ phức tạp, khái niệm 'Human-in-the-Loop' không được đánh đồng thành một vai trò chung chung. Bốn vai trò con người (CS, Quản lý, QA, Chuyên viên gian lận) sở hữu 4 thẩm quyền, tiếp cận 4 luồng thông tin khác nhau và tạo ra 4 đầu ra nghiệp vụ độc lập. Sự phân định này đảm bảo tính kiểm soát nội bộ và quản trị rủi ro chặt chẽ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Mental Models &amp; Human-in-the-Loop Workflows &amp; COSO Enterprise Risk Management (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -1087,10 +1185,25 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nêu đơn vị được sửa, phần giữ nguyên và cách khôi phục.
-Phân tích theo nguyên lý thiết kế: Nêu đơn vị được sửa, phần giữ nguyên và cách khôi phục.</t>
+- 1.0 điểm: Xác định đơn vị chỉnh sửa theo 4 khối độc lập (Tiêu đề, Mở đầu, Nội dung, CTA).
+- 1.0 điểm: Quy định rõ cơ chế giữ nguyên vẹn các khối đã chấp nhận khi tạo lại khối CTA.
+- 1.0 điểm: Thiết kế cơ chế khôi phục lịch sử (Local Undo / Version Stack per block) để quay lại bản cũ dễ dàng.
+- 1.0 điểm: Bảo đảm trải nghiệm người dùng không bị mất mát công sức đã chỉnh sửa trước đó.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Cơ chế Chỉnh sửa Từng phần và Quản lý Phiên bản (Modular Editability Design):
+1. Đơn vị được phép chỉnh sửa độc lập (Modular Editing Units):
+- Chia nhỏ email thành 4 khối (blocks) độc lập trên giao diện: Block 1: `Tiêu đề (Subject)`, Block 2: `Lời mở đầu (Greeting)`, Block 3: `Nội dung chính (Body)`, Block 4: `Lời kêu gọi hành động (Call-to-Action - CTA)`.
+- Mỗi khối có nút thao tác riêng: [Sửa chữ trực tiếp], [Tạo lại khối này], [Khóa / Ghim nội dung].
+2. Phần giữ nguyên tuyệt đối khi thử nghiệm phương án mới:
+- Khi người dùng bấm 'Thử phương án mới' tại Khối Lời kêu gọi hành động (CTA), hệ thống tự động khóa (Lock) và giữ nguyên vẹn 100% nội dung của 3 khối còn lại (Tiêu đề, Lời mở đầu, Nội dung chính).
+- Ngữ cảnh của 3 khối đã chấp nhận được truyền vào prompt làm ràng buộc cố định (fixed context) để AI sinh ra CTA mới hài hòa và đồng nhất về văn phong.
+3. Cơ chế Khôi phục và Quản lý Lịch sử (Undo / Version History per Block):
+- Ngăn chứa lịch sử riêng cho từng khối (Local History Stack per Block): Riêng tại khối CTA, hiển thị thanh điều hướng lịch sử phiên bản: `Bản 1 (gốc)` | `Bản 2 (mới tạo)` | `Bản 3`.
+- Người dùng có thể dễ dàng bấm qua lại giữa các phiên bản CTA hoặc bấm nút 'Hoàn tác' (Undo / Revert to previous) để quay lại bản trước đó ngay lập tức mà hoàn toàn không ảnh hưởng đến bất kỳ ký tự nào của phần còn lại trong email.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Output Editability Design trong sản phẩm AI đòi hỏi cấu trúc hóa đầu ra thành các khối mô-đun (Granular Modules) thay vì một khối văn bản nguyên khối. Việc cung cấp khả năng khóa vùng đã chọn và lưu lịch sử hoàn tác riêng cho từng khối giúp giảm thiểu sự thất vọng của người dùng, trao quyền kiểm soát linh hoạt và tối ưu hóa thời gian tương tác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Microsoft HAX Toolkit - Guideline 10: Support efficient correction &amp; Guideline 11: Scope services when in doubt (https://www.microsoft.com/en-us/research/project/guidelines-for-human-ai-interaction/)</t>
         </is>
       </c>
     </row>
@@ -1175,10 +1288,37 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Văn bản cuối không cho biết AI đã tạo gì trước khi người dùng sửa.
-Phân tích theo nguyên lý thiết kế: Văn bản cuối không cho biết AI đã tạo gì trước khi người dùng sửa.</t>
+- 1.0 điểm: Thiết kế schema bản ghi tối thiểu gồm đầy đủ: Output gốc của AI, Output sau khi sửa của người dùng, và Diff patch.
+- 1.0 điểm: Bổ sung các metadata quan trọng (timestamp, user_id, document context ID, loại lỗi thực thể).
+- 1.0 điểm: Nêu rõ vị trí sử dụng trong bộ kiểm thử vàng (Golden Evaluation Benchmark) để đo tỷ lệ ảo giác thực thể.
+- 1.0 điểm: Tích hợp vào quy trình CI/CD làm bài kiểm thử hồi quy (Regression test) chống lặp lại lỗi.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đặc tả Bản ghi Tối thiểu Dữ liệu Chỉnh sửa (Correction Signal Event Schema):
+```json
+{
+  "event_id": "evt_corr_98412",
+  "timestamp": "2026-10-23T15:30:00Z",
+  "user_id": "usr_8832",
+  "task_id": "doc_summary_772",
+  "original_ai_output": "Lan chịu trách nhiệm chính về việc triển khai dự án.",
+  "user_corrected_output": "Minh chịu trách nhiệm chính về việc triển khai dự án.",
+  "diff_patch": {
+    "operation": "REPLACE",
+    "target_span": "Lan",
+    "replacement": "Minh",
+    "char_offset": [0, 3]
+  },
+  "context_document_id": "meeting_minutes_v1",
+  "correction_type": "ENTITY_SUBSTITUTION"
+}
+```
+2. Nơi sử dụng Dữ liệu Chỉnh sửa cho Bộ Đánh giá (Evaluation &amp; Learning Engine):
+- Tự động mở rộng Bộ đề Kiểm thử Vàng (Golden Eval Set Expansion): Cặp dữ liệu `(Tài liệu gốc, Câu hỏi, Câu sai: 'Lan...', Câu đúng: 'Minh...')` được chuyển thẳng vào hàng đợi của bộ dữ liệu đánh giá thực thể (Named Entity Resolution Test Suite). Bộ đánh giá sẽ dùng ca này để đo lường tỷ lệ ảo giác gán sai thực thể (Entity Attribution Error Rate).
+- Phân tích Lỗi Hồi quy (Regression Testing): Đưa ca sửa đổi này vào pipeline kiểm thử tự động CI/CD để đảm bảo khi cập nhật prompt hoặc model mới trong tương lai, mô hình không bao giờ lặp lại lỗi gán nhầm người phụ trách trên biên bản cuộc họp này nữa.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Dữ liệu chỉnh sửa của người dùng (Implicit Correction Signals) là mỏ vàng quý giá nhất để cải tiến hệ thống AI. Một bản ghi chỉnh sửa chuẩn mực bắt buộc phải lưu trữ đồng thời bản gốc của AI, bản sửa của người dùng, và diff patch cụ thể. Dữ liệu này được kết nối trực tiếp vào bộ eval benchmark để ngăn chặn lỗi tái diễn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Feedback + Learning (Capturing Implicit Feedback) &amp; Data-Centric AI Practices (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -1258,10 +1398,26 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng gộp mọi lỗi thành 'câu trả lời kém chất lượng'.
-Phân tích theo nguyên lý thiết kế: Đừng gộp mọi lỗi thành 'câu trả lời kém chất lượng'.</t>
+- 1.0 điểm: Phân chia chính xác thành 2 nhóm lỗi riêng biệt: Bịa đặt chính sách hoàn tiền (2 lỗi) và Sai giọng điệu (2 lỗi).
+- 1.0 điểm: Xếp ưu tiên xử lý số 1 cho lỗi bịa đặt chính sách kèm lập luận chặt chẽ về rủi ro tài chính và pháp lý.
+- 1.0 điểm: Đề xuất bước cải tiến kỹ thuật trực diện (RAG grounding, prompt constraint, refuse to answer if absent).
+- 1.0 điểm: Thiết lập bài test kiểm chứng cụ thể (10 test cases bẫy hoàn tiền) với tiêu chí đạt 0% ảo giác.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại các Nhóm lỗi Định tính (Qualitative Error Clustering):
+- Nhóm Lỗi 1: Bịa đặt Thông tin Chính sách Hoàn tiền (Hallucination / Critical Factual Fabrication) - Số lượng: 2 lỗi.
+  + Bản chất: Mô hình tự tạo ra các điều khoản hoàn tiền không có trong quy định của công ty (ví dụ: hứa hẹn hoàn tiền 100% sau 60 ngày).
+- Nhóm Lỗi 2: Lệch Chuẩn Giọng điệu Giao tiếp (Tone &amp; Empathy Inconsistency / Soft Style Deviation) - Số lượng: 2 lỗi.
+  + Bản chất: Câu trả lời đúng về mặt thông tin nhưng sử dụng từ ngữ cộc lốc, thiếu sự đồng cảm hoặc quá máy móc đối với khách hàng đang bức xúc.
+2. Xếp thứ tự Ưu tiên Xử lý (Prioritization based on Severity &amp; Impact):
+- ƯU TIÊN 1 (MỨC ĐỘ KHẨN CẤP CAO NHẤT): Nhóm Lỗi 1 (Bịa đặt chính sách hoàn tiền). Lý do: Đây là lỗi rủi ro tài chính và pháp lý nghiêm trọng. Việc hứa hẹn sai chính sách hoàn tiền có thể khiến công ty chịu tổn thất ngân sách trực tiếp, vi phạm cam kết thương mại và dẫn đến khiếu nại pháp lý của khách hàng.
+- ƯU TIÊN 2 (MỨC ĐỘ TRUNG BÌNH): Nhóm Lỗi 2 (Sai giọng điệu). Lý do: Lỗi này ảnh hưởng đến trải nghiệm cảm xúc và hình ảnh thương hiệu, nhưng không gây thất thoát tài chính trực tiếp ngay lập tức.
+3. Bước Cải tiến và Kiểm chứng Đầu tiên cho Nhóm Ưu tiên 1:
+- Bước cải tiến: Tích hợp chốt chặn RAG bắt buộc (Strict Grounding / Knowledge Retrieval Guardrail). Trong System Prompt, bổ sung chỉ thị nghiêm ngặt: 'Chỉ được trích dẫn chính sách hoàn tiền từ tài liệu chính thức được cung cấp trong thẻ &lt;policy&gt;; nếu dữ liệu không có, bắt buộc phải trả lời chưa có thông tin và chuyển sang nhân viên hỗ trợ; tuyệt đối không tự đưa ra thời hạn hay số tiền'.
+- Bước kiểm chứng: Xây dựng bộ test case gồm 10 câu hỏi mẹo về hoàn tiền không có trong tài liệu và chạy đánh giá tự động (Factual Consistency Check) để xác nhận tỷ lệ bịa đặt chính sách giảm về đúng 0%.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiểm toán chất lượng sản phẩm AI, việc gộp chung các lỗi thành 'câu trả lời kém chất lượng' sẽ làm tê liệt quá trình ra quyết định. Bắt buộc phải phân nhóm lỗi theo mức độ nghiêm trọng (Severity): Lỗi bịa đặt tài chính/pháp lý luôn đứng đầu ma trận ưu tiên xử lý trước các lỗi về phong cách diễn đạt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Managing Errors + Safety &amp; Risk-Weighted Defect Prioritization in AI Products (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1498,28 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tỷ lệ mở email không nói đoạn nào sai hoặc cần sửa thế nào.
-Phân tích theo nguyên lý thiết kế: Tỷ lệ mở email không nói đoạn nào sai hoặc cần sửa thế nào.</t>
+- 1.0 điểm: Chọn đúng tín hiệu phản hồi cục bộ theo đoạn văn (In-line highlighting / Quick tone tagging).
+- 1.0 điểm: Định nghĩa đầy đủ schema sự kiện telemetry (draft_id, text_span, tone_issue, replacement).
+- 1.0 điểm: Thiết kế cơ chế giảm thiểu công sức người dùng (micro-interaction, menu nổi 1-click).
+- 1.0 điểm: Phân tích sâu sắc phần mơ hồ còn lại (tính chủ quan văn hóa và mối quan hệ cá nhân giữa các bên).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Tín hiệu Phản hồi Mới (New Granular Feedback Signal):
+- Tín hiệu được chọn: Tín hiệu đánh dấu văn bản và phản hồi cục bộ trong văn cảnh (In-line Text Highlighting &amp; Quick Tone Flagging).
+2. Định nghĩa Sự kiện và Dữ liệu đi kèm (Telemetry Event Payload):
+- Tên sự kiện: `draft_tone_feedback_submitted`.
+- Dữ liệu đi kèm (Payload):
+  + `draft_id` &amp; `user_id`: Định danh bản nháp và người dùng.
+  + `highlighted_text_span`: Đoạn câu văn cụ thể mà người dùng bôi đen (ví dụ: 'Bạn phải làm việc này ngay').
+  + `selected_tone_issue`: Thẻ phân loại nhanh người dùng chọn từ menu ngữ cảnh: `[Quá cộc lốc]`, `[Quá trịnh trọng]`, `[Thiếu đồng cảm]`, `[Gây áp lực]`.
+  + `user_replacement_text`: Nội dung người dùng gõ đè lên (nếu có).
+3. Công sức người dùng cần bỏ ra (User Friction / Effort):
+- Công sức cực kỳ thấp (Micro-effort / One-click): Khi người dùng bôi đen câu văn cảm thấy phản cảm, một menu nổi (floating tooltip) nhỏ lập tức xuất hiện ngay cạnh con trỏ chuột với 3 nút bấm phân loại giọng điệu; người dùng chỉ mất 1 cú nhấp chuột (dưới 1 giây) mà không phải gõ phím viết giải thích dài dòng.
+4. Phần Mơ hồ Còn lại (Remaining Ambiguity):
+- Nhận thức về 'giọng điệu phù hợp' mang tính chủ quan cao và phụ thuộc sâu sắc vào mối quan hệ văn hóa giữa người gửi và người nhận (ví dụ: một câu văn có thể bị người này cho là 'cộc lốc', nhưng người khác lại thấy là 'ngắn gọn, hiệu quả'). Tín hiệu thu thập được không thể phản ánh trọn vẹn ngữ cảnh quan hệ cá nhân ngoài đời thực giữa hai bên.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Chỉ số cấp cao như Tỷ lệ mở email (Open Rate) hoàn toàn vô dụng để chẩn đoán lỗi giọng điệu của AI vì nó chịu tác động bởi tiêu đề và uy tín người gửi, không phản ánh chất lượng câu chữ bên trong. Một tín hiệu phản hồi cục bộ (In-line highlighting) giúp định vị chính xác vị trí và bản chất lỗi với mức độ ma sát tương tác thấp nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google PAIR Guidebook - Feedback + Learning (Explicit vs. Implicit Feedback Mechanics) (https://pair.withgoogle.com/guidebook/)</t>
         </is>
       </c>
     </row>
